--- a/results/Int All Data 0.6/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.6/Linea_fi_explain.xlsx
@@ -1760,7 +1760,7 @@
         <v>0.05734624596382245</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0001874145969491304</v>
+        <v>0.0001976552523510767</v>
       </c>
       <c r="AE3" t="n">
         <v>0.002010379119293684</v>
@@ -1817,7 +1817,7 @@
         <v>0.00269674874737928</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.004453042706994346</v>
+        <v>0.004448264876129559</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0002630126824548783</v>
@@ -1829,7 +1829,7 @@
         <v>0.003335392692704372</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.003718226991273638</v>
+        <v>0.003723459853649358</v>
       </c>
       <c r="BB3" t="n">
         <v>0.003498209652134446</v>
@@ -1844,7 +1844,7 @@
         <v>0.001853813006695533</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.003163603976518351</v>
+        <v>0.003163556198392323</v>
       </c>
       <c r="BG3" t="n">
         <v>0.002223233343036828</v>
@@ -1892,7 +1892,7 @@
         <v>0.002448513466612575</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0007388238825152605</v>
+        <v>0.0007335910201395413</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0001271355907610716</v>
@@ -1901,10 +1901,10 @@
         <v>0.003149818034279496</v>
       </c>
       <c r="BY3" t="n">
+        <v>0.0006970664397950311</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0.0007018950250195601</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.0006970664397950311</v>
       </c>
       <c r="CA3" t="n">
         <v>0.003720362391572488</v>
@@ -1913,7 +1913,7 @@
         <v>0.008146815463017784</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.006327210817888342</v>
+        <v>0.006332487862743224</v>
       </c>
       <c r="CD3" t="n">
         <v>0.00189276018415623</v>
@@ -1922,7 +1922,7 @@
         <v>-0.001140375625006204</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.00123388651461888</v>
+        <v>-0.001228653652243162</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4100048855142889</v>
@@ -2090,10 +2090,10 @@
         <v>0.009999279346655959</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.007790334319270896</v>
+        <v>0.007795454646971868</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.02428838953857807</v>
+        <v>0.0242832692108771</v>
       </c>
       <c r="EL3" t="n">
         <v>4.247806103246932e-06</v>
@@ -2229,7 +2229,7 @@
         <v>0.04928513607131333</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005550975906037202</v>
+        <v>0.005547431385977378</v>
       </c>
       <c r="AE4" t="n">
         <v>0.003672497589207755</v>
@@ -2286,7 +2286,7 @@
         <v>0.004375976376249622</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00697287464492374</v>
+        <v>0.006973662206205356</v>
       </c>
       <c r="AX4" t="n">
         <v>0.001254805889298056</v>
@@ -2298,7 +2298,7 @@
         <v>0.004535023358097886</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01059581541321383</v>
+        <v>0.01059823848990364</v>
       </c>
       <c r="BB4" t="n">
         <v>0.01115038178987692</v>
@@ -2313,7 +2313,7 @@
         <v>0.006057505295905738</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.008056671107995904</v>
+        <v>0.008042852550010473</v>
       </c>
       <c r="BG4" t="n">
         <v>0.008886422000067387</v>
@@ -2361,7 +2361,7 @@
         <v>0.00846412931789693</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.005888042580637736</v>
+        <v>0.005884970786796444</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0002625279805069099</v>
@@ -2370,10 +2370,10 @@
         <v>0.008421379202166807</v>
       </c>
       <c r="BY4" t="n">
+        <v>0.003392707393932913</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>0.003399497454218406</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.003392707393932913</v>
       </c>
       <c r="CA4" t="n">
         <v>0.008461227154844483</v>
@@ -2382,7 +2382,7 @@
         <v>0.01279456893544737</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.02193742175335953</v>
+        <v>0.02194065916191233</v>
       </c>
       <c r="CD4" t="n">
         <v>0.008803514558956808</v>
@@ -2391,7 +2391,7 @@
         <v>0.005253362800384764</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002545740123828544</v>
+        <v>0.002548849146942714</v>
       </c>
       <c r="CG4" t="n">
         <v>0.09843516847458694</v>
@@ -2559,10 +2559,10 @@
         <v>0.01811099012657959</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.02223752690005143</v>
+        <v>0.02223550032249946</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.04490235233311118</v>
+        <v>0.0449054649891807</v>
       </c>
       <c r="EL4" t="n">
         <v>3.616007878108925e-05</v>
@@ -3167,7 +3167,7 @@
         <v>0.02577096456980395</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.00419059971589153</v>
+        <v>-0.004164998077386664</v>
       </c>
       <c r="AE6" t="n">
         <v>-0.0001317592143128598</v>
@@ -3251,7 +3251,7 @@
         <v>0.0009363089510102229</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.0008342292319501871</v>
+        <v>-0.0007977506327283973</v>
       </c>
       <c r="BG6" t="n">
         <v>-0.003481899941480284</v>
@@ -3798,7 +3798,7 @@
         <v>0.0001830093779698394</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0001800728844013444</v>
+        <v>-0.0001800728844013499</v>
       </c>
       <c r="CG7" t="n">
         <v>0.3934630246928879</v>
@@ -4162,7 +4162,7 @@
         <v>0.004755438822030203</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.006234213377317768</v>
+        <v>0.006222268800155801</v>
       </c>
       <c r="AX8" t="n">
         <v>0.0004656363253698365</v>
@@ -4237,7 +4237,7 @@
         <v>0.006020595800797951</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0048693534248584</v>
+        <v>0.004856271268919102</v>
       </c>
       <c r="BW8" t="n">
         <v>0.0003012645528569002</v>
@@ -4246,10 +4246,10 @@
         <v>0.005079914569396113</v>
       </c>
       <c r="BY8" t="n">
+        <v>0.003852871869838781</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>0.003889086259022748</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.003852871869838781</v>
       </c>
       <c r="CA8" t="n">
         <v>0.007951301275535592</v>
@@ -4267,7 +4267,7 @@
         <v>0.001108036883654637</v>
       </c>
       <c r="CF8" t="n">
-        <v>7.849293563578775e-05</v>
+        <v>0.0001177394034536816</v>
       </c>
       <c r="CG8" t="n">
         <v>0.4907438855741024</v>
@@ -4658,7 +4658,7 @@
         <v>0.01199575371549891</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01949901768172884</v>
+        <v>0.01944990176817284</v>
       </c>
       <c r="BG9" t="n">
         <v>0.02054467271858579</v>
